--- a/input/Data_Demand_drivers.xlsx
+++ b/input/Data_Demand_drivers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\draft_endemo\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\endemo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A816A4-E416-4DBB-AFF7-CCE03EB68375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040450BF-5D52-4F39-A58E-F9AEB9DAA31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -801,7 +801,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -819,13 +819,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -844,6 +837,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1950,96 +1949,6 @@
       <c r="E3" t="s">
         <v>151</v>
       </c>
-      <c r="P3">
-        <v>17894.296685502479</v>
-      </c>
-      <c r="Q3">
-        <v>18421.04218147607</v>
-      </c>
-      <c r="R3">
-        <v>19121.497892289499</v>
-      </c>
-      <c r="S3">
-        <v>19972.025407234622</v>
-      </c>
-      <c r="T3">
-        <v>20141.939475319428</v>
-      </c>
-      <c r="U3">
-        <v>20041.947992263897</v>
-      </c>
-      <c r="V3">
-        <v>21124.255695091233</v>
-      </c>
-      <c r="W3">
-        <v>21880.807628135564</v>
-      </c>
-      <c r="X3">
-        <v>22558.714790358026</v>
-      </c>
-      <c r="Y3">
-        <v>23484.599191830675</v>
-      </c>
-      <c r="Z3">
-        <v>23766.107651562979</v>
-      </c>
-      <c r="AA3">
-        <v>23855.525856973836</v>
-      </c>
-      <c r="AB3">
-        <v>23783.945487006444</v>
-      </c>
-      <c r="AC3">
-        <v>24221.34037474346</v>
-      </c>
-      <c r="AD3">
-        <v>24991.33368351117</v>
-      </c>
-      <c r="AE3">
-        <v>25630.332997633614</v>
-      </c>
-      <c r="AF3">
-        <v>26204.589578531355</v>
-      </c>
-      <c r="AG3">
-        <v>26531.229705288002</v>
-      </c>
-      <c r="AH3">
-        <v>27407.520066196255</v>
-      </c>
-      <c r="AI3">
-        <v>28256.106220973092</v>
-      </c>
-      <c r="AJ3">
-        <v>29485.709974488083</v>
-      </c>
-      <c r="AK3">
-        <v>30766.928957772732</v>
-      </c>
-      <c r="AL3">
-        <v>31121.070565007587</v>
-      </c>
-      <c r="AM3">
-        <v>30615.140211743532</v>
-      </c>
-      <c r="AN3">
-        <v>31238.879059662766</v>
-      </c>
-      <c r="AO3">
-        <v>31628.159813094277</v>
-      </c>
-      <c r="AP3">
-        <v>31790.866859605634</v>
-      </c>
-      <c r="AQ3">
-        <v>32313.297070434404</v>
-      </c>
-      <c r="AR3">
-        <v>32959.073569141772</v>
-      </c>
-      <c r="AS3">
-        <v>33559.399373749926</v>
-      </c>
       <c r="AT3">
         <v>34490.075768861861</v>
       </c>
@@ -3144,382 +3053,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:17" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="9"/>
+      <c r="F6" s="12"/>
+      <c r="I6" s="12"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23" t="s">
+      <c r="J9" s="20"/>
+      <c r="K9" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="L9" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23" t="s">
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11" t="s">
+      <c r="D10" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11" t="s">
+      <c r="J10" t="s">
         <v>195</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
+      <c r="B11" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11" t="s">
+      <c r="D11" t="s">
         <v>164</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11" t="s">
+      <c r="I11" t="s">
         <v>151</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" t="s">
         <v>168</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11" t="s">
+      <c r="L11" t="s">
         <v>169</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11" t="s">
+      <c r="Q11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
+      <c r="B12" t="s">
         <v>184</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11" t="s">
+      <c r="D12" t="s">
         <v>176</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="15">
         <v>45110.958333333336</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" t="s">
         <v>182</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" t="s">
         <v>183</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11" t="s">
+      <c r="D13" t="s">
         <v>185</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11" t="s">
+      <c r="H13" t="s">
         <v>188</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" t="s">
         <v>189</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="B15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" t="s">
         <v>200</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" t="s">
         <v>201</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="11" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" t="s">
         <v>205</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="11" t="s">
+      <c r="B17" t="s">
         <v>202</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11" t="s">
+      <c r="D17" t="s">
         <v>206</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="15"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
+      <c r="B18" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11" t="s">
+      <c r="D18" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="11" t="s">
+      <c r="B19" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11" t="s">
+      <c r="D19" t="s">
         <v>208</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
